--- a/data/ranking_times_base_TOP600_LIMPO.xlsx
+++ b/data/ranking_times_base_TOP600_LIMPO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anderson\Documents\GitHub\Skynet-V18\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC37B46-F31F-420E-A511-B0FF6812E599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED5F5D2E-8796-4D5A-843F-DE718098F3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="17520" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17160" yWindow="-120" windowWidth="19440" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ranking" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2892" uniqueCount="892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2895" uniqueCount="892">
   <si>
     <t>Country</t>
   </si>
@@ -1843,9 +1843,6 @@
     <t>Penafiel</t>
   </si>
   <si>
-    <t>FIFA Club World Cup</t>
-  </si>
-  <si>
     <t>Benfica</t>
   </si>
   <si>
@@ -2699,6 +2696,9 @@
   </si>
   <si>
     <t>Al Kuwait</t>
+  </si>
+  <si>
+    <t>PSV</t>
   </si>
 </sst>
 </file>
@@ -3066,7 +3066,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P693"/>
+  <dimension ref="A1:P694"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
@@ -3305,13 +3305,13 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>769</v>
+      </c>
+      <c r="B7" t="s">
         <v>770</v>
       </c>
-      <c r="B7" t="s">
-        <v>771</v>
-      </c>
       <c r="C7" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D7">
         <v>11</v>
@@ -3363,13 +3363,13 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B9" t="s">
         <v>295</v>
       </c>
       <c r="C9" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D9">
         <v>11</v>
@@ -3500,13 +3500,13 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B13" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C13" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D13">
         <v>13</v>
@@ -3529,13 +3529,13 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>806</v>
+      </c>
+      <c r="B14" t="s">
         <v>807</v>
       </c>
-      <c r="B14" t="s">
-        <v>808</v>
-      </c>
       <c r="C14" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="D14">
         <v>10</v>
@@ -3703,13 +3703,13 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B20" t="s">
         <v>117</v>
       </c>
       <c r="C20" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D20">
         <v>35</v>
@@ -3732,13 +3732,13 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B21" t="s">
         <v>201</v>
       </c>
       <c r="C21" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="D21">
         <v>15</v>
@@ -3956,13 +3956,13 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>806</v>
+      </c>
+      <c r="B28" t="s">
         <v>807</v>
       </c>
-      <c r="B28" t="s">
-        <v>808</v>
-      </c>
       <c r="C28" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D28">
         <v>8</v>
@@ -3985,13 +3985,13 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B29" t="s">
         <v>201</v>
       </c>
       <c r="C29" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="D29">
         <v>11</v>
@@ -4072,13 +4072,13 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B32" t="s">
         <v>201</v>
       </c>
       <c r="C32" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D32">
         <v>14</v>
@@ -4107,13 +4107,13 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B33" t="s">
         <v>265</v>
       </c>
       <c r="C33" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D33">
         <v>6</v>
@@ -4165,13 +4165,13 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B35" t="s">
         <v>79</v>
       </c>
       <c r="C35" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D35">
         <v>14</v>
@@ -4194,13 +4194,13 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B36" t="s">
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D36">
         <v>6</v>
@@ -4368,13 +4368,13 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>806</v>
+      </c>
+      <c r="B42" t="s">
         <v>807</v>
       </c>
-      <c r="B42" t="s">
-        <v>808</v>
-      </c>
       <c r="C42" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D42">
         <v>5</v>
@@ -4484,13 +4484,13 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B46" t="s">
         <v>562</v>
       </c>
       <c r="C46" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D46">
         <v>13</v>
@@ -4513,13 +4513,13 @@
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B47" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C47" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D47">
         <v>12</v>
@@ -4542,13 +4542,13 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>715</v>
+      </c>
+      <c r="B48" t="s">
         <v>716</v>
       </c>
-      <c r="B48" t="s">
-        <v>717</v>
-      </c>
       <c r="C48" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D48">
         <v>11</v>
@@ -4600,13 +4600,13 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B50" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C50" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D50">
         <v>4</v>
@@ -4658,13 +4658,13 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B52" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C52" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D52">
         <v>22</v>
@@ -4774,13 +4774,13 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B56" t="s">
         <v>17</v>
       </c>
       <c r="C56" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D56">
         <v>8</v>
@@ -4919,13 +4919,13 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>769</v>
+      </c>
+      <c r="B61" t="s">
         <v>770</v>
       </c>
-      <c r="B61" t="s">
-        <v>771</v>
-      </c>
       <c r="C61" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="D61">
         <v>5</v>
@@ -4948,13 +4948,13 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B62" t="s">
         <v>17</v>
       </c>
       <c r="C62" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D62">
         <v>5</v>
@@ -4977,13 +4977,13 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B63" t="s">
         <v>201</v>
       </c>
       <c r="C63" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D63">
         <v>15</v>
@@ -5041,13 +5041,13 @@
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B65" t="s">
         <v>310</v>
       </c>
       <c r="C65" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D65">
         <v>10</v>
@@ -5207,13 +5207,13 @@
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>709</v>
+      </c>
+      <c r="B70" t="s">
         <v>710</v>
       </c>
-      <c r="B70" t="s">
-        <v>711</v>
-      </c>
       <c r="C70" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D70">
         <v>7</v>
@@ -5410,13 +5410,13 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B77" t="s">
         <v>231</v>
       </c>
       <c r="C77" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D77">
         <v>25</v>
@@ -5468,13 +5468,13 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B79" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C79" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D79">
         <v>7</v>
@@ -5497,13 +5497,13 @@
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B80" t="s">
         <v>562</v>
       </c>
       <c r="C80" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D80">
         <v>11</v>
@@ -5613,13 +5613,13 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B84" t="s">
         <v>222</v>
       </c>
       <c r="C84" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D84">
         <v>9</v>
@@ -5787,13 +5787,13 @@
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B90" t="s">
         <v>201</v>
       </c>
       <c r="C90" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D90">
         <v>13</v>
@@ -5816,13 +5816,13 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>780</v>
+      </c>
+      <c r="B91" t="s">
         <v>781</v>
       </c>
-      <c r="B91" t="s">
-        <v>782</v>
-      </c>
       <c r="C91" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D91">
         <v>10</v>
@@ -5845,13 +5845,13 @@
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B92" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C92" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D92">
         <v>7</v>
@@ -5990,13 +5990,13 @@
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B97" t="s">
         <v>201</v>
       </c>
       <c r="C97" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="D97">
         <v>11</v>
@@ -6141,13 +6141,13 @@
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B102" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C102" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="D102">
         <v>11</v>
@@ -6170,13 +6170,13 @@
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B103" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C103" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -6220,13 +6220,13 @@
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B104" t="s">
         <v>273</v>
       </c>
       <c r="C104" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D104">
         <v>19</v>
@@ -6249,13 +6249,13 @@
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B105" t="s">
         <v>201</v>
       </c>
       <c r="C105" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="D105">
         <v>12</v>
@@ -6400,13 +6400,13 @@
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B110" t="s">
         <v>562</v>
       </c>
       <c r="C110" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D110">
         <v>12</v>
@@ -6545,13 +6545,13 @@
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B115" t="s">
         <v>222</v>
       </c>
       <c r="C115" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D115">
         <v>11</v>
@@ -6574,13 +6574,13 @@
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>806</v>
+      </c>
+      <c r="B116" t="s">
         <v>807</v>
       </c>
-      <c r="B116" t="s">
-        <v>808</v>
-      </c>
       <c r="C116" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D116">
         <v>9</v>
@@ -6661,13 +6661,13 @@
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>780</v>
+      </c>
+      <c r="B119" t="s">
         <v>781</v>
       </c>
-      <c r="B119" t="s">
-        <v>782</v>
-      </c>
       <c r="C119" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D119">
         <v>9</v>
@@ -6690,13 +6690,13 @@
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>715</v>
+      </c>
+      <c r="B120" t="s">
         <v>716</v>
       </c>
-      <c r="B120" t="s">
-        <v>717</v>
-      </c>
       <c r="C120" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D120">
         <v>8</v>
@@ -6719,13 +6719,13 @@
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B121" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C121" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D121">
         <v>8</v>
@@ -6748,13 +6748,13 @@
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B122" t="s">
+        <v>873</v>
+      </c>
+      <c r="C122" t="s">
         <v>874</v>
-      </c>
-      <c r="C122" t="s">
-        <v>875</v>
       </c>
       <c r="D122">
         <v>11</v>
@@ -6789,7 +6789,7 @@
         <v>297</v>
       </c>
       <c r="C123" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="D123">
         <v>8</v>
@@ -6876,13 +6876,13 @@
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>672</v>
+      </c>
+      <c r="B126" t="s">
         <v>673</v>
       </c>
-      <c r="B126" t="s">
-        <v>674</v>
-      </c>
       <c r="C126" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D126">
         <v>10</v>
@@ -6905,13 +6905,13 @@
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B127" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C127" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="D127">
         <v>19</v>
@@ -6940,7 +6940,7 @@
         <v>21</v>
       </c>
       <c r="C128" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D128">
         <v>8</v>
@@ -7127,13 +7127,13 @@
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B133" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C133" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D133">
         <v>9</v>
@@ -7214,13 +7214,13 @@
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B136" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C136" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="D136">
         <v>5</v>
@@ -7243,13 +7243,13 @@
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>715</v>
+      </c>
+      <c r="B137" t="s">
         <v>716</v>
       </c>
-      <c r="B137" t="s">
-        <v>717</v>
-      </c>
       <c r="C137" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D137">
         <v>12</v>
@@ -7301,13 +7301,13 @@
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>806</v>
+      </c>
+      <c r="B139" t="s">
         <v>807</v>
       </c>
-      <c r="B139" t="s">
-        <v>808</v>
-      </c>
       <c r="C139" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D139">
         <v>8</v>
@@ -7330,13 +7330,13 @@
     </row>
     <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B140" t="s">
         <v>581</v>
       </c>
       <c r="C140" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D140">
         <v>7</v>
@@ -7388,13 +7388,13 @@
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B142" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C142" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D142">
         <v>4</v>
@@ -7446,13 +7446,13 @@
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B144" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C144" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="D144">
         <v>6</v>
@@ -7539,7 +7539,7 @@
         <v>602</v>
       </c>
       <c r="C147" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D147">
         <v>11</v>
@@ -7678,13 +7678,13 @@
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B152" t="s">
         <v>25</v>
       </c>
       <c r="C152" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D152">
         <v>13</v>
@@ -7736,13 +7736,13 @@
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B154" t="s">
         <v>265</v>
       </c>
       <c r="C154" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D154">
         <v>10</v>
@@ -7794,13 +7794,13 @@
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B156" t="s">
         <v>17</v>
       </c>
       <c r="C156" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D156">
         <v>7</v>
@@ -7852,13 +7852,13 @@
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B158" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C158" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D158">
         <v>4</v>
@@ -7910,13 +7910,13 @@
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B160" t="s">
         <v>265</v>
       </c>
       <c r="C160" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D160">
         <v>15</v>
@@ -7939,13 +7939,13 @@
     </row>
     <row r="161" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>681</v>
+      </c>
+      <c r="B161" t="s">
         <v>682</v>
       </c>
-      <c r="B161" t="s">
-        <v>683</v>
-      </c>
       <c r="C161" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D161">
         <v>4</v>
@@ -8084,13 +8084,13 @@
     </row>
     <row r="166" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B166" t="s">
+        <v>850</v>
+      </c>
+      <c r="C166" t="s">
         <v>851</v>
-      </c>
-      <c r="C166" t="s">
-        <v>852</v>
       </c>
       <c r="D166">
         <v>8</v>
@@ -8113,13 +8113,13 @@
     </row>
     <row r="167" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>733</v>
+      </c>
+      <c r="B167" t="s">
         <v>734</v>
       </c>
-      <c r="B167" t="s">
-        <v>735</v>
-      </c>
       <c r="C167" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D167">
         <v>8</v>
@@ -8171,13 +8171,13 @@
     </row>
     <row r="169" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B169" t="s">
         <v>295</v>
       </c>
       <c r="C169" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D169">
         <v>8</v>
@@ -8287,13 +8287,13 @@
     </row>
     <row r="173" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
+        <v>769</v>
+      </c>
+      <c r="B173" t="s">
         <v>770</v>
       </c>
-      <c r="B173" t="s">
-        <v>771</v>
-      </c>
       <c r="C173" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D173">
         <v>4</v>
@@ -8316,13 +8316,13 @@
     </row>
     <row r="174" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B174" t="s">
         <v>222</v>
       </c>
       <c r="C174" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D174">
         <v>7</v>
@@ -8438,7 +8438,7 @@
         <v>602</v>
       </c>
       <c r="C178" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D178">
         <v>5</v>
@@ -8519,13 +8519,13 @@
     </row>
     <row r="181" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>617</v>
+      </c>
+      <c r="B181" t="s">
         <v>618</v>
       </c>
-      <c r="B181" t="s">
-        <v>619</v>
-      </c>
       <c r="C181" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D181">
         <v>12</v>
@@ -8577,13 +8577,13 @@
     </row>
     <row r="183" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B183" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C183" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D183">
         <v>6</v>
@@ -8693,13 +8693,13 @@
     </row>
     <row r="187" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B187" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C187" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D187">
         <v>9</v>
@@ -8722,13 +8722,13 @@
     </row>
     <row r="188" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B188" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C188" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="D188">
         <v>10</v>
@@ -8801,13 +8801,13 @@
     </row>
     <row r="190" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B190" t="s">
+        <v>762</v>
+      </c>
+      <c r="C190" t="s">
         <v>763</v>
-      </c>
-      <c r="C190" t="s">
-        <v>764</v>
       </c>
       <c r="D190">
         <v>6</v>
@@ -8946,13 +8946,13 @@
     </row>
     <row r="195" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
+        <v>780</v>
+      </c>
+      <c r="B195" t="s">
         <v>781</v>
       </c>
-      <c r="B195" t="s">
-        <v>782</v>
-      </c>
       <c r="C195" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D195">
         <v>9</v>
@@ -9033,13 +9033,13 @@
     </row>
     <row r="198" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B198" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C198" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D198">
         <v>8</v>
@@ -9097,7 +9097,7 @@
         <v>201</v>
       </c>
       <c r="C200" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D200">
         <v>13</v>
@@ -9213,13 +9213,13 @@
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B204" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C204" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D204">
         <v>8</v>
@@ -9358,13 +9358,13 @@
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B209" t="s">
         <v>25</v>
       </c>
       <c r="C209" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D209">
         <v>11</v>
@@ -9416,13 +9416,13 @@
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B211" t="s">
         <v>581</v>
       </c>
       <c r="C211" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D211">
         <v>5</v>
@@ -9561,13 +9561,13 @@
     </row>
     <row r="216" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B216" t="s">
         <v>283</v>
       </c>
       <c r="C216" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D216">
         <v>13</v>
@@ -9677,13 +9677,13 @@
     </row>
     <row r="220" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B220" t="s">
         <v>295</v>
       </c>
       <c r="C220" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D220">
         <v>13</v>
@@ -10046,13 +10046,13 @@
     </row>
     <row r="232" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B232" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C232" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D232">
         <v>13</v>
@@ -10075,13 +10075,13 @@
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B233" t="s">
         <v>362</v>
       </c>
       <c r="C233" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D233">
         <v>10</v>
@@ -10200,7 +10200,7 @@
         <v>452</v>
       </c>
       <c r="B237" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C237" t="s">
         <v>454</v>
@@ -10232,7 +10232,7 @@
         <v>21</v>
       </c>
       <c r="C238" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D238">
         <v>9</v>
@@ -10406,13 +10406,13 @@
     </row>
     <row r="244" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B244" t="s">
         <v>17</v>
       </c>
       <c r="C244" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D244">
         <v>4</v>
@@ -10435,13 +10435,13 @@
     </row>
     <row r="245" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B245" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C245" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D245">
         <v>17</v>
@@ -10464,13 +10464,13 @@
     </row>
     <row r="246" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B246" t="s">
+        <v>812</v>
+      </c>
+      <c r="C246" t="s">
         <v>813</v>
-      </c>
-      <c r="C246" t="s">
-        <v>814</v>
       </c>
       <c r="D246">
         <v>9</v>
@@ -10493,13 +10493,13 @@
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
+        <v>769</v>
+      </c>
+      <c r="B247" t="s">
         <v>770</v>
       </c>
-      <c r="B247" t="s">
-        <v>771</v>
-      </c>
       <c r="C247" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="D247">
         <v>13</v>
@@ -10528,7 +10528,7 @@
         <v>602</v>
       </c>
       <c r="C248" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D248">
         <v>6</v>
@@ -10754,13 +10754,13 @@
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B256" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C256" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D256">
         <v>4</v>
@@ -10868,7 +10868,7 @@
         <v>602</v>
       </c>
       <c r="C259" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D259">
         <v>18</v>
@@ -11036,13 +11036,13 @@
     </row>
     <row r="265" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B265" t="s">
         <v>581</v>
       </c>
       <c r="C265" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D265">
         <v>6</v>
@@ -11065,13 +11065,13 @@
     </row>
     <row r="266" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B266" t="s">
         <v>115</v>
       </c>
       <c r="C266" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="D266">
         <v>14</v>
@@ -11173,13 +11173,13 @@
     </row>
     <row r="269" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
+        <v>806</v>
+      </c>
+      <c r="B269" t="s">
         <v>807</v>
       </c>
-      <c r="B269" t="s">
-        <v>808</v>
-      </c>
       <c r="C269" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="D269">
         <v>10</v>
@@ -11202,13 +11202,13 @@
     </row>
     <row r="270" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B270" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C270" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D270">
         <v>11</v>
@@ -11237,13 +11237,13 @@
     </row>
     <row r="271" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
+        <v>780</v>
+      </c>
+      <c r="B271" t="s">
         <v>781</v>
       </c>
-      <c r="B271" t="s">
-        <v>782</v>
-      </c>
       <c r="C271" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D271">
         <v>4</v>
@@ -11295,13 +11295,13 @@
     </row>
     <row r="273" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
+        <v>709</v>
+      </c>
+      <c r="B273" t="s">
         <v>710</v>
       </c>
-      <c r="B273" t="s">
-        <v>711</v>
-      </c>
       <c r="C273" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D273">
         <v>7</v>
@@ -11490,13 +11490,13 @@
     </row>
     <row r="279" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
+        <v>681</v>
+      </c>
+      <c r="B279" t="s">
         <v>682</v>
       </c>
-      <c r="B279" t="s">
-        <v>683</v>
-      </c>
       <c r="C279" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D279">
         <v>12</v>
@@ -11627,13 +11627,13 @@
     </row>
     <row r="283" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
+        <v>672</v>
+      </c>
+      <c r="B283" t="s">
         <v>673</v>
       </c>
-      <c r="B283" t="s">
-        <v>674</v>
-      </c>
       <c r="C283" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D283">
         <v>7</v>
@@ -11714,13 +11714,13 @@
     </row>
     <row r="286" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B286" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C286" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="D286">
         <v>12</v>
@@ -11743,13 +11743,13 @@
     </row>
     <row r="287" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B287" t="s">
         <v>201</v>
       </c>
       <c r="C287" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="D287">
         <v>6</v>
@@ -11807,7 +11807,7 @@
         <v>602</v>
       </c>
       <c r="C289" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D289">
         <v>16</v>
@@ -11830,13 +11830,13 @@
     </row>
     <row r="290" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
+        <v>672</v>
+      </c>
+      <c r="B290" t="s">
         <v>673</v>
       </c>
-      <c r="B290" t="s">
-        <v>674</v>
-      </c>
       <c r="C290" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D290">
         <v>15</v>
@@ -11888,13 +11888,13 @@
     </row>
     <row r="292" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B292" t="s">
         <v>17</v>
       </c>
       <c r="C292" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D292">
         <v>4</v>
@@ -11917,13 +11917,13 @@
     </row>
     <row r="293" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
+        <v>780</v>
+      </c>
+      <c r="B293" t="s">
         <v>781</v>
       </c>
-      <c r="B293" t="s">
-        <v>782</v>
-      </c>
       <c r="C293" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="D293">
         <v>12</v>
@@ -11946,13 +11946,13 @@
     </row>
     <row r="294" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B294" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C294" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="D294">
         <v>10</v>
@@ -12120,13 +12120,13 @@
     </row>
     <row r="300" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
+        <v>709</v>
+      </c>
+      <c r="B300" t="s">
         <v>710</v>
       </c>
-      <c r="B300" t="s">
-        <v>711</v>
-      </c>
       <c r="C300" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D300">
         <v>12</v>
@@ -12257,13 +12257,13 @@
     </row>
     <row r="304" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B304" t="s">
         <v>222</v>
       </c>
       <c r="C304" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D304">
         <v>7</v>
@@ -12315,13 +12315,13 @@
     </row>
     <row r="306" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B306" t="s">
         <v>273</v>
       </c>
       <c r="C306" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D306">
         <v>4</v>
@@ -12460,13 +12460,13 @@
     </row>
     <row r="311" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B311" t="s">
         <v>201</v>
       </c>
       <c r="C311" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="D311">
         <v>5</v>
@@ -12626,13 +12626,13 @@
     </row>
     <row r="316" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B316" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C316" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D316">
         <v>9</v>
@@ -12719,13 +12719,13 @@
     </row>
     <row r="319" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B319" t="s">
         <v>201</v>
       </c>
       <c r="C319" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="D319">
         <v>9</v>
@@ -12864,13 +12864,13 @@
     </row>
     <row r="324" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B324" t="s">
         <v>17</v>
       </c>
       <c r="C324" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D324">
         <v>4</v>
@@ -12899,7 +12899,7 @@
         <v>602</v>
       </c>
       <c r="C325" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D325">
         <v>7</v>
@@ -13009,13 +13009,13 @@
     </row>
     <row r="329" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B329" t="s">
         <v>201</v>
       </c>
       <c r="C329" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="D329">
         <v>11</v>
@@ -13096,13 +13096,13 @@
     </row>
     <row r="332" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B332" t="s">
         <v>362</v>
       </c>
       <c r="C332" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="D332">
         <v>8</v>
@@ -13218,13 +13218,13 @@
     </row>
     <row r="336" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
+        <v>688</v>
+      </c>
+      <c r="B336" t="s">
+        <v>876</v>
+      </c>
+      <c r="C336" t="s">
         <v>689</v>
-      </c>
-      <c r="B336" t="s">
-        <v>877</v>
-      </c>
-      <c r="C336" t="s">
-        <v>690</v>
       </c>
       <c r="D336">
         <v>11</v>
@@ -13471,13 +13471,13 @@
     </row>
     <row r="344" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B344" t="s">
         <v>453</v>
       </c>
       <c r="C344" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D344">
         <v>4</v>
@@ -13500,13 +13500,13 @@
     </row>
     <row r="345" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B345" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C345" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="D345">
         <v>5</v>
@@ -13608,13 +13608,13 @@
     </row>
     <row r="348" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
+        <v>780</v>
+      </c>
+      <c r="B348" t="s">
         <v>781</v>
       </c>
-      <c r="B348" t="s">
-        <v>782</v>
-      </c>
       <c r="C348" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="D348">
         <v>8</v>
@@ -13898,13 +13898,13 @@
     </row>
     <row r="358" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
+        <v>867</v>
+      </c>
+      <c r="B358" t="s">
         <v>868</v>
       </c>
-      <c r="B358" t="s">
+      <c r="C358" t="s">
         <v>869</v>
-      </c>
-      <c r="C358" t="s">
-        <v>870</v>
       </c>
       <c r="D358">
         <v>14</v>
@@ -13933,13 +13933,13 @@
     </row>
     <row r="359" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B359" t="s">
         <v>295</v>
       </c>
       <c r="C359" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D359">
         <v>9</v>
@@ -13991,13 +13991,13 @@
     </row>
     <row r="361" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B361" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C361" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D361">
         <v>8</v>
@@ -14078,13 +14078,13 @@
     </row>
     <row r="364" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
+        <v>715</v>
+      </c>
+      <c r="B364" t="s">
         <v>716</v>
       </c>
-      <c r="B364" t="s">
-        <v>717</v>
-      </c>
       <c r="C364" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D364">
         <v>4</v>
@@ -14223,13 +14223,13 @@
     </row>
     <row r="369" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B369" t="s">
         <v>231</v>
       </c>
       <c r="C369" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D369">
         <v>15</v>
@@ -14281,13 +14281,13 @@
     </row>
     <row r="371" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B371" t="s">
         <v>581</v>
       </c>
       <c r="C371" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D371">
         <v>4</v>
@@ -14513,13 +14513,13 @@
     </row>
     <row r="379" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B379" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C379" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="D379">
         <v>5</v>
@@ -14658,13 +14658,13 @@
     </row>
     <row r="384" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
+        <v>715</v>
+      </c>
+      <c r="B384" t="s">
         <v>716</v>
       </c>
-      <c r="B384" t="s">
-        <v>717</v>
-      </c>
       <c r="C384" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D384">
         <v>10</v>
@@ -14774,13 +14774,13 @@
     </row>
     <row r="388" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B388" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C388" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D388">
         <v>6</v>
@@ -14832,13 +14832,13 @@
     </row>
     <row r="390" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B390" t="s">
         <v>581</v>
       </c>
       <c r="C390" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D390">
         <v>6</v>
@@ -14861,13 +14861,13 @@
     </row>
     <row r="391" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B391" t="s">
         <v>265</v>
       </c>
       <c r="C391" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D391">
         <v>8</v>
@@ -15006,13 +15006,13 @@
     </row>
     <row r="396" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
+        <v>780</v>
+      </c>
+      <c r="B396" t="s">
         <v>781</v>
       </c>
-      <c r="B396" t="s">
-        <v>782</v>
-      </c>
       <c r="C396" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="D396">
         <v>15</v>
@@ -15114,13 +15114,13 @@
     </row>
     <row r="399" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B399" t="s">
+        <v>783</v>
+      </c>
+      <c r="C399" t="s">
         <v>784</v>
-      </c>
-      <c r="C399" t="s">
-        <v>785</v>
       </c>
       <c r="D399">
         <v>6</v>
@@ -15172,13 +15172,13 @@
     </row>
     <row r="401" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
+        <v>715</v>
+      </c>
+      <c r="B401" t="s">
         <v>716</v>
       </c>
-      <c r="B401" t="s">
-        <v>717</v>
-      </c>
       <c r="C401" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D401">
         <v>4</v>
@@ -15230,13 +15230,13 @@
     </row>
     <row r="403" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B403" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C403" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D403">
         <v>5</v>
@@ -15317,13 +15317,13 @@
     </row>
     <row r="406" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
+        <v>806</v>
+      </c>
+      <c r="B406" t="s">
         <v>807</v>
       </c>
-      <c r="B406" t="s">
-        <v>808</v>
-      </c>
       <c r="C406" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D406">
         <v>4</v>
@@ -15346,13 +15346,13 @@
     </row>
     <row r="407" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
+        <v>867</v>
+      </c>
+      <c r="B407" t="s">
         <v>868</v>
       </c>
-      <c r="B407" t="s">
-        <v>869</v>
-      </c>
       <c r="C407" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D407">
         <v>9</v>
@@ -15474,7 +15474,7 @@
         <v>602</v>
       </c>
       <c r="C411" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D411">
         <v>7</v>
@@ -15497,13 +15497,13 @@
     </row>
     <row r="412" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
+        <v>672</v>
+      </c>
+      <c r="B412" t="s">
         <v>673</v>
       </c>
-      <c r="B412" t="s">
-        <v>674</v>
-      </c>
       <c r="C412" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D412">
         <v>6</v>
@@ -15555,13 +15555,13 @@
     </row>
     <row r="414" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B414" t="s">
         <v>581</v>
       </c>
       <c r="C414" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D414">
         <v>6</v>
@@ -15613,13 +15613,13 @@
     </row>
     <row r="416" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B416" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C416" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D416">
         <v>12</v>
@@ -15642,13 +15642,13 @@
     </row>
     <row r="417" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B417" t="s">
         <v>265</v>
       </c>
       <c r="C417" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D417">
         <v>7</v>
@@ -15700,13 +15700,13 @@
     </row>
     <row r="419" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B419" t="s">
         <v>371</v>
       </c>
       <c r="C419" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D419">
         <v>18</v>
@@ -15729,13 +15729,13 @@
     </row>
     <row r="420" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B420" t="s">
         <v>562</v>
       </c>
       <c r="C420" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D420">
         <v>16</v>
@@ -15874,13 +15874,13 @@
     </row>
     <row r="425" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B425" t="s">
         <v>201</v>
       </c>
       <c r="C425" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D425">
         <v>8</v>
@@ -15915,7 +15915,7 @@
         <v>602</v>
       </c>
       <c r="C426" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D426">
         <v>4</v>
@@ -15938,13 +15938,13 @@
     </row>
     <row r="427" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B427" t="s">
         <v>265</v>
       </c>
       <c r="C427" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D427">
         <v>5</v>
@@ -16083,13 +16083,13 @@
     </row>
     <row r="432" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B432" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C432" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D432">
         <v>8</v>
@@ -16249,13 +16249,13 @@
     </row>
     <row r="437" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B437" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C437" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D437">
         <v>7</v>
@@ -16336,13 +16336,13 @@
     </row>
     <row r="440" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B440" t="s">
         <v>310</v>
       </c>
       <c r="C440" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D440">
         <v>14</v>
@@ -16365,13 +16365,13 @@
     </row>
     <row r="441" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
+        <v>709</v>
+      </c>
+      <c r="B441" t="s">
         <v>710</v>
       </c>
-      <c r="B441" t="s">
+      <c r="C441" t="s">
         <v>711</v>
-      </c>
-      <c r="C441" t="s">
-        <v>712</v>
       </c>
       <c r="D441">
         <v>6</v>
@@ -16394,13 +16394,13 @@
     </row>
     <row r="442" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B442" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C442" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D442">
         <v>25</v>
@@ -16481,13 +16481,13 @@
     </row>
     <row r="445" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
+        <v>806</v>
+      </c>
+      <c r="B445" t="s">
         <v>807</v>
       </c>
-      <c r="B445" t="s">
-        <v>808</v>
-      </c>
       <c r="C445" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D445">
         <v>6</v>
@@ -16618,13 +16618,13 @@
     </row>
     <row r="449" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B449" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C449" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D449">
         <v>7</v>
@@ -16726,13 +16726,13 @@
     </row>
     <row r="452" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B452" t="s">
         <v>79</v>
       </c>
       <c r="C452" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D452">
         <v>8</v>
@@ -16813,13 +16813,13 @@
     </row>
     <row r="455" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B455" t="s">
         <v>581</v>
       </c>
       <c r="C455" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D455">
         <v>4</v>
@@ -16871,13 +16871,13 @@
     </row>
     <row r="457" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B457" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C457" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D457">
         <v>11</v>
@@ -16900,13 +16900,13 @@
     </row>
     <row r="458" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B458" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C458" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="D458">
         <v>11</v>
@@ -16964,13 +16964,13 @@
     </row>
     <row r="460" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B460" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C460" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D460">
         <v>8</v>
@@ -17151,13 +17151,13 @@
     </row>
     <row r="465" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B465" t="s">
         <v>17</v>
       </c>
       <c r="C465" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="D465">
         <v>9</v>
@@ -17180,13 +17180,13 @@
     </row>
     <row r="466" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B466" t="s">
+        <v>719</v>
+      </c>
+      <c r="C466" t="s">
         <v>720</v>
-      </c>
-      <c r="C466" t="s">
-        <v>721</v>
       </c>
       <c r="D466">
         <v>5</v>
@@ -17296,13 +17296,13 @@
     </row>
     <row r="470" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B470" t="s">
+        <v>818</v>
+      </c>
+      <c r="C470" t="s">
         <v>819</v>
-      </c>
-      <c r="C470" t="s">
-        <v>820</v>
       </c>
       <c r="D470">
         <v>6</v>
@@ -17375,13 +17375,13 @@
     </row>
     <row r="472" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B472" t="s">
         <v>17</v>
       </c>
       <c r="C472" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D472">
         <v>6</v>
@@ -17439,7 +17439,7 @@
         <v>602</v>
       </c>
       <c r="C474" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D474">
         <v>7</v>
@@ -17541,13 +17541,13 @@
     </row>
     <row r="477" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
+        <v>672</v>
+      </c>
+      <c r="B477" t="s">
         <v>673</v>
       </c>
-      <c r="B477" t="s">
-        <v>674</v>
-      </c>
       <c r="C477" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D477">
         <v>5</v>
@@ -17599,13 +17599,13 @@
     </row>
     <row r="479" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B479" t="s">
+        <v>659</v>
+      </c>
+      <c r="C479" t="s">
         <v>660</v>
-      </c>
-      <c r="C479" t="s">
-        <v>661</v>
       </c>
       <c r="D479">
         <v>17</v>
@@ -17657,13 +17657,13 @@
     </row>
     <row r="481" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B481" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C481" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D481">
         <v>6</v>
@@ -17686,13 +17686,13 @@
     </row>
     <row r="482" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B482" t="s">
         <v>365</v>
       </c>
       <c r="C482" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D482">
         <v>15</v>
@@ -17765,13 +17765,13 @@
     </row>
     <row r="484" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
+        <v>888</v>
+      </c>
+      <c r="B484" t="s">
         <v>889</v>
       </c>
-      <c r="B484" t="s">
+      <c r="C484" t="s">
         <v>890</v>
-      </c>
-      <c r="C484" t="s">
-        <v>891</v>
       </c>
       <c r="D484">
         <v>8</v>
@@ -17800,13 +17800,13 @@
     </row>
     <row r="485" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
+        <v>769</v>
+      </c>
+      <c r="B485" t="s">
         <v>770</v>
       </c>
-      <c r="B485" t="s">
-        <v>771</v>
-      </c>
       <c r="C485" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D485">
         <v>7</v>
@@ -17887,13 +17887,13 @@
     </row>
     <row r="488" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B488" t="s">
+        <v>800</v>
+      </c>
+      <c r="C488" t="s">
         <v>801</v>
-      </c>
-      <c r="C488" t="s">
-        <v>802</v>
       </c>
       <c r="D488">
         <v>6</v>
@@ -17945,13 +17945,13 @@
     </row>
     <row r="490" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B490" t="s">
         <v>201</v>
       </c>
       <c r="C490" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D490">
         <v>12</v>
@@ -17974,13 +17974,13 @@
     </row>
     <row r="491" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B491" t="s">
         <v>362</v>
       </c>
       <c r="C491" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D491">
         <v>9</v>
@@ -18009,13 +18009,13 @@
     </row>
     <row r="492" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B492" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C492" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D492">
         <v>4</v>
@@ -18038,13 +18038,13 @@
     </row>
     <row r="493" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B493" t="s">
         <v>17</v>
       </c>
       <c r="C493" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D493">
         <v>5</v>
@@ -18125,13 +18125,13 @@
     </row>
     <row r="496" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
+        <v>617</v>
+      </c>
+      <c r="B496" t="s">
         <v>618</v>
       </c>
-      <c r="B496" t="s">
-        <v>619</v>
-      </c>
       <c r="C496" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D496">
         <v>6</v>
@@ -18183,13 +18183,13 @@
     </row>
     <row r="498" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B498" t="s">
         <v>17</v>
       </c>
       <c r="C498" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D498">
         <v>8</v>
@@ -18241,13 +18241,13 @@
     </row>
     <row r="500" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
+        <v>681</v>
+      </c>
+      <c r="B500" t="s">
         <v>682</v>
       </c>
-      <c r="B500" t="s">
-        <v>683</v>
-      </c>
       <c r="C500" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D500">
         <v>4</v>
@@ -18357,13 +18357,13 @@
     </row>
     <row r="504" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B504" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C504" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D504">
         <v>9</v>
@@ -18523,13 +18523,13 @@
     </row>
     <row r="509" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B509" t="s">
         <v>79</v>
       </c>
       <c r="C509" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D509">
         <v>4</v>
@@ -18552,13 +18552,13 @@
     </row>
     <row r="510" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B510" t="s">
         <v>562</v>
       </c>
       <c r="C510" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D510">
         <v>10</v>
@@ -18581,13 +18581,13 @@
     </row>
     <row r="511" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
+        <v>630</v>
+      </c>
+      <c r="B511" t="s">
         <v>631</v>
       </c>
-      <c r="B511" t="s">
-        <v>632</v>
-      </c>
       <c r="C511" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D511">
         <v>9</v>
@@ -18610,13 +18610,13 @@
     </row>
     <row r="512" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B512" t="s">
         <v>117</v>
       </c>
       <c r="C512" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D512">
         <v>25</v>
@@ -18703,7 +18703,7 @@
         <v>604</v>
       </c>
       <c r="C515" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D515">
         <v>6</v>
@@ -18834,13 +18834,13 @@
     </row>
     <row r="519" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B519" t="s">
         <v>581</v>
       </c>
       <c r="C519" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D519">
         <v>10</v>
@@ -18863,13 +18863,13 @@
     </row>
     <row r="520" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B520" t="s">
         <v>295</v>
       </c>
       <c r="C520" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D520">
         <v>8</v>
@@ -18950,13 +18950,13 @@
     </row>
     <row r="523" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B523" t="s">
         <v>201</v>
       </c>
       <c r="C523" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="D523">
         <v>9</v>
@@ -19145,13 +19145,13 @@
     </row>
     <row r="529" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B529" t="s">
         <v>17</v>
       </c>
       <c r="C529" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D529">
         <v>7</v>
@@ -19174,13 +19174,13 @@
     </row>
     <row r="530" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B530" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C530" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D530">
         <v>4</v>
@@ -19488,10 +19488,10 @@
         <v>601</v>
       </c>
       <c r="B540" t="s">
+        <v>602</v>
+      </c>
+      <c r="C540" t="s">
         <v>606</v>
-      </c>
-      <c r="C540" t="s">
-        <v>607</v>
       </c>
       <c r="D540">
         <v>14</v>
@@ -19730,13 +19730,13 @@
     </row>
     <row r="547" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B547" t="s">
         <v>201</v>
       </c>
       <c r="C547" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="D547">
         <v>4</v>
@@ -19788,13 +19788,13 @@
     </row>
     <row r="549" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
+        <v>715</v>
+      </c>
+      <c r="B549" t="s">
         <v>716</v>
       </c>
-      <c r="B549" t="s">
-        <v>717</v>
-      </c>
       <c r="C549" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D549">
         <v>7</v>
@@ -19904,13 +19904,13 @@
     </row>
     <row r="553" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
+        <v>780</v>
+      </c>
+      <c r="B553" t="s">
         <v>781</v>
       </c>
-      <c r="B553" t="s">
+      <c r="C553" t="s">
         <v>782</v>
-      </c>
-      <c r="C553" t="s">
-        <v>783</v>
       </c>
       <c r="D553">
         <v>4</v>
@@ -19933,13 +19933,13 @@
     </row>
     <row r="554" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
+        <v>672</v>
+      </c>
+      <c r="B554" t="s">
         <v>673</v>
       </c>
-      <c r="B554" t="s">
-        <v>674</v>
-      </c>
       <c r="C554" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D554">
         <v>7</v>
@@ -20107,13 +20107,13 @@
     </row>
     <row r="560" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
+        <v>617</v>
+      </c>
+      <c r="B560" t="s">
         <v>618</v>
       </c>
-      <c r="B560" t="s">
-        <v>619</v>
-      </c>
       <c r="C560" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D560">
         <v>4</v>
@@ -20223,13 +20223,13 @@
     </row>
     <row r="564" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B564" t="s">
         <v>201</v>
       </c>
       <c r="C564" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="D564">
         <v>10</v>
@@ -20252,13 +20252,13 @@
     </row>
     <row r="565" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
+        <v>617</v>
+      </c>
+      <c r="B565" t="s">
         <v>618</v>
       </c>
-      <c r="B565" t="s">
-        <v>619</v>
-      </c>
       <c r="C565" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D565">
         <v>20</v>
@@ -20505,13 +20505,13 @@
     </row>
     <row r="573" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B573" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C573" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D573">
         <v>10</v>
@@ -20642,13 +20642,13 @@
     </row>
     <row r="577" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
+        <v>769</v>
+      </c>
+      <c r="B577" t="s">
         <v>770</v>
       </c>
-      <c r="B577" t="s">
-        <v>771</v>
-      </c>
       <c r="C577" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D577">
         <v>9</v>
@@ -20787,13 +20787,13 @@
     </row>
     <row r="582" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B582" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C582" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D582">
         <v>9</v>
@@ -20874,13 +20874,13 @@
     </row>
     <row r="585" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B585" t="s">
+        <v>743</v>
+      </c>
+      <c r="C585" t="s">
         <v>744</v>
-      </c>
-      <c r="C585" t="s">
-        <v>745</v>
       </c>
       <c r="D585">
         <v>7</v>
@@ -21164,13 +21164,13 @@
     </row>
     <row r="595" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
+        <v>630</v>
+      </c>
+      <c r="B595" t="s">
         <v>631</v>
       </c>
-      <c r="B595" t="s">
-        <v>632</v>
-      </c>
       <c r="C595" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D595">
         <v>10</v>
@@ -21280,13 +21280,13 @@
     </row>
     <row r="599" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B599" t="s">
         <v>17</v>
       </c>
       <c r="C599" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D599">
         <v>12</v>
@@ -21512,13 +21512,13 @@
     </row>
     <row r="607" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B607" t="s">
         <v>310</v>
       </c>
       <c r="C607" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D607">
         <v>14</v>
@@ -21599,13 +21599,13 @@
     </row>
     <row r="610" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B610" t="s">
+        <v>741</v>
+      </c>
+      <c r="C610" t="s">
         <v>742</v>
-      </c>
-      <c r="C610" t="s">
-        <v>743</v>
       </c>
       <c r="D610">
         <v>5</v>
@@ -21657,13 +21657,13 @@
     </row>
     <row r="612" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
+        <v>806</v>
+      </c>
+      <c r="B612" t="s">
         <v>807</v>
       </c>
-      <c r="B612" t="s">
-        <v>808</v>
-      </c>
       <c r="C612" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D612">
         <v>5</v>
@@ -21852,13 +21852,13 @@
     </row>
     <row r="618" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
+        <v>715</v>
+      </c>
+      <c r="B618" t="s">
         <v>716</v>
       </c>
-      <c r="B618" t="s">
+      <c r="C618" t="s">
         <v>717</v>
-      </c>
-      <c r="C618" t="s">
-        <v>718</v>
       </c>
       <c r="D618">
         <v>5</v>
@@ -21881,13 +21881,13 @@
     </row>
     <row r="619" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
+        <v>681</v>
+      </c>
+      <c r="B619" t="s">
         <v>682</v>
       </c>
-      <c r="B619" t="s">
-        <v>683</v>
-      </c>
       <c r="C619" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D619">
         <v>4</v>
@@ -21939,13 +21939,13 @@
     </row>
     <row r="621" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B621" t="s">
         <v>310</v>
       </c>
       <c r="C621" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D621">
         <v>9</v>
@@ -21968,13 +21968,13 @@
     </row>
     <row r="622" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
+        <v>630</v>
+      </c>
+      <c r="B622" t="s">
         <v>631</v>
       </c>
-      <c r="B622" t="s">
+      <c r="C622" t="s">
         <v>632</v>
-      </c>
-      <c r="C622" t="s">
-        <v>633</v>
       </c>
       <c r="D622">
         <v>6</v>
@@ -22026,13 +22026,13 @@
     </row>
     <row r="624" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B624" t="s">
         <v>58</v>
       </c>
       <c r="C624" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D624">
         <v>4</v>
@@ -22084,13 +22084,13 @@
     </row>
     <row r="626" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B626" t="s">
         <v>79</v>
       </c>
       <c r="C626" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D626">
         <v>16</v>
@@ -22142,13 +22142,13 @@
     </row>
     <row r="628" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
+        <v>769</v>
+      </c>
+      <c r="B628" t="s">
         <v>770</v>
       </c>
-      <c r="B628" t="s">
-        <v>771</v>
-      </c>
       <c r="C628" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D628">
         <v>6</v>
@@ -22511,13 +22511,13 @@
     </row>
     <row r="640" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
+        <v>733</v>
+      </c>
+      <c r="B640" t="s">
         <v>734</v>
       </c>
-      <c r="B640" t="s">
-        <v>735</v>
-      </c>
       <c r="C640" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D640">
         <v>7</v>
@@ -22640,13 +22640,13 @@
     </row>
     <row r="643" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B643" t="s">
         <v>115</v>
       </c>
       <c r="C643" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D643">
         <v>15</v>
@@ -22690,13 +22690,13 @@
     </row>
     <row r="644" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B644" t="s">
+        <v>809</v>
+      </c>
+      <c r="C644" t="s">
         <v>810</v>
-      </c>
-      <c r="C644" t="s">
-        <v>811</v>
       </c>
       <c r="D644">
         <v>8</v>
@@ -22990,13 +22990,13 @@
     </row>
     <row r="650" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
+        <v>733</v>
+      </c>
+      <c r="B650" t="s">
         <v>734</v>
       </c>
-      <c r="B650" t="s">
-        <v>735</v>
-      </c>
       <c r="C650" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D650">
         <v>12</v>
@@ -23040,13 +23040,13 @@
     </row>
     <row r="651" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
+        <v>672</v>
+      </c>
+      <c r="B651" t="s">
         <v>673</v>
       </c>
-      <c r="B651" t="s">
+      <c r="C651" t="s">
         <v>674</v>
-      </c>
-      <c r="C651" t="s">
-        <v>675</v>
       </c>
       <c r="D651">
         <v>7</v>
@@ -23090,13 +23090,13 @@
     </row>
     <row r="652" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
+        <v>806</v>
+      </c>
+      <c r="B652" t="s">
         <v>807</v>
       </c>
-      <c r="B652" t="s">
+      <c r="C652" t="s">
         <v>808</v>
-      </c>
-      <c r="C652" t="s">
-        <v>809</v>
       </c>
       <c r="D652">
         <v>7</v>
@@ -23240,13 +23240,13 @@
     </row>
     <row r="655" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B655" t="s">
         <v>581</v>
       </c>
       <c r="C655" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D655">
         <v>7</v>
@@ -23290,13 +23290,13 @@
     </row>
     <row r="656" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B656" t="s">
         <v>17</v>
       </c>
       <c r="C656" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D656">
         <v>5</v>
@@ -23790,13 +23790,13 @@
     </row>
     <row r="666" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
+        <v>681</v>
+      </c>
+      <c r="B666" t="s">
         <v>682</v>
       </c>
-      <c r="B666" t="s">
+      <c r="C666" t="s">
         <v>683</v>
-      </c>
-      <c r="C666" t="s">
-        <v>684</v>
       </c>
       <c r="D666">
         <v>6</v>
@@ -23840,13 +23840,13 @@
     </row>
     <row r="667" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B667" t="s">
         <v>581</v>
       </c>
       <c r="C667" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D667">
         <v>4</v>
@@ -23890,13 +23890,13 @@
     </row>
     <row r="668" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B668" t="s">
         <v>581</v>
       </c>
       <c r="C668" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D668">
         <v>4</v>
@@ -23990,13 +23990,13 @@
     </row>
     <row r="670" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
+        <v>733</v>
+      </c>
+      <c r="B670" t="s">
         <v>734</v>
       </c>
-      <c r="B670" t="s">
-        <v>735</v>
-      </c>
       <c r="C670" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D670">
         <v>6</v>
@@ -24040,13 +24040,13 @@
     </row>
     <row r="671" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B671" t="s">
         <v>79</v>
       </c>
       <c r="C671" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D671">
         <v>22</v>
@@ -24090,13 +24090,13 @@
     </row>
     <row r="672" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
+        <v>617</v>
+      </c>
+      <c r="B672" t="s">
         <v>618</v>
       </c>
-      <c r="B672" t="s">
+      <c r="C672" t="s">
         <v>619</v>
-      </c>
-      <c r="C672" t="s">
-        <v>620</v>
       </c>
       <c r="D672">
         <v>8</v>
@@ -24490,13 +24490,13 @@
     </row>
     <row r="680" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
+        <v>769</v>
+      </c>
+      <c r="B680" t="s">
         <v>770</v>
       </c>
-      <c r="B680" t="s">
-        <v>771</v>
-      </c>
       <c r="C680" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D680">
         <v>9</v>
@@ -24590,13 +24590,13 @@
     </row>
     <row r="682" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B682" t="s">
         <v>79</v>
       </c>
       <c r="C682" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D682">
         <v>13</v>
@@ -24640,13 +24640,13 @@
     </row>
     <row r="683" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B683" t="s">
+        <v>736</v>
+      </c>
+      <c r="C683" t="s">
         <v>737</v>
-      </c>
-      <c r="C683" t="s">
-        <v>738</v>
       </c>
       <c r="D683">
         <v>7</v>
@@ -24690,13 +24690,13 @@
     </row>
     <row r="684" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B684" t="s">
         <v>562</v>
       </c>
       <c r="C684" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D684">
         <v>21</v>
@@ -24840,13 +24840,13 @@
     </row>
     <row r="687" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
+        <v>769</v>
+      </c>
+      <c r="B687" t="s">
         <v>770</v>
       </c>
-      <c r="B687" t="s">
+      <c r="C687" t="s">
         <v>771</v>
-      </c>
-      <c r="C687" t="s">
-        <v>772</v>
       </c>
       <c r="D687">
         <v>9</v>
@@ -24890,13 +24890,13 @@
     </row>
     <row r="688" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
+        <v>733</v>
+      </c>
+      <c r="B688" t="s">
         <v>734</v>
       </c>
-      <c r="B688" t="s">
+      <c r="C688" t="s">
         <v>735</v>
-      </c>
-      <c r="C688" t="s">
-        <v>736</v>
       </c>
       <c r="D688">
         <v>7</v>
@@ -24990,13 +24990,13 @@
     </row>
     <row r="690" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B690" t="s">
         <v>17</v>
       </c>
       <c r="C690" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D690">
         <v>10</v>
@@ -25186,6 +25186,32 @@
       </c>
       <c r="P693" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="694" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A694" t="s">
+        <v>540</v>
+      </c>
+      <c r="B694" t="s">
+        <v>541</v>
+      </c>
+      <c r="C694" t="s">
+        <v>891</v>
+      </c>
+      <c r="D694">
+        <v>1</v>
+      </c>
+      <c r="E694">
+        <v>1</v>
+      </c>
+      <c r="F694">
+        <v>1</v>
+      </c>
+      <c r="G694">
+        <v>111.11</v>
+      </c>
+      <c r="H694">
+        <v>1111</v>
       </c>
     </row>
   </sheetData>

--- a/data/ranking_times_base_TOP600_LIMPO.xlsx
+++ b/data/ranking_times_base_TOP600_LIMPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anderson\Documents\GitHub\Skynet-V18\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A94059F8-EEC3-469F-AB0D-579DE50ABC9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749B9C62-DEEA-4880-982F-59CFBC419F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17160" yWindow="-120" windowWidth="19440" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3066,7 +3066,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:P694"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3167,7 +3166,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>294</v>
       </c>
@@ -3196,7 +3195,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>63</v>
       </c>
@@ -3283,7 +3282,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>769</v>
       </c>
@@ -3341,7 +3340,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>653</v>
       </c>
@@ -3399,7 +3398,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>580</v>
       </c>
@@ -3486,7 +3485,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>806</v>
       </c>
@@ -3573,7 +3572,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>510</v>
       </c>
@@ -3602,7 +3601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>455</v>
       </c>
@@ -3631,7 +3630,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>63</v>
       </c>
@@ -3660,7 +3659,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>700</v>
       </c>
@@ -3689,7 +3688,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>855</v>
       </c>
@@ -3718,7 +3717,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>92</v>
       </c>
@@ -3747,7 +3746,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>294</v>
       </c>
@@ -3805,7 +3804,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>198</v>
       </c>
@@ -3863,7 +3862,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>294</v>
       </c>
@@ -3892,7 +3891,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>806</v>
       </c>
@@ -3921,7 +3920,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>855</v>
       </c>
@@ -3950,7 +3949,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -3979,7 +3978,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>294</v>
       </c>
@@ -4008,7 +4007,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>865</v>
       </c>
@@ -4043,7 +4042,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>617</v>
       </c>
@@ -4101,7 +4100,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>637</v>
       </c>
@@ -4130,7 +4129,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>690</v>
       </c>
@@ -4159,7 +4158,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>92</v>
       </c>
@@ -4217,7 +4216,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>193</v>
       </c>
@@ -4246,7 +4245,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>198</v>
       </c>
@@ -4275,7 +4274,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>20</v>
       </c>
@@ -4304,7 +4303,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>806</v>
       </c>
@@ -4333,7 +4332,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>294</v>
       </c>
@@ -4391,7 +4390,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>588</v>
       </c>
@@ -4420,7 +4419,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>653</v>
       </c>
@@ -4449,7 +4448,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>760</v>
       </c>
@@ -4507,7 +4506,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>294</v>
       </c>
@@ -4536,7 +4535,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>733</v>
       </c>
@@ -4623,7 +4622,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>510</v>
       </c>
@@ -4681,7 +4680,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>286</v>
       </c>
@@ -4710,7 +4709,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>792</v>
       </c>
@@ -4797,7 +4796,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>198</v>
       </c>
@@ -4826,7 +4825,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>294</v>
       </c>
@@ -4855,7 +4854,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>769</v>
       </c>
@@ -4884,7 +4883,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>690</v>
       </c>
@@ -4913,7 +4912,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>863</v>
       </c>
@@ -4948,7 +4947,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>510</v>
       </c>
@@ -4977,7 +4976,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>653</v>
       </c>
@@ -5006,7 +5005,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>580</v>
       </c>
@@ -5035,7 +5034,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>294</v>
       </c>
@@ -5093,7 +5092,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>20</v>
       </c>
@@ -5143,7 +5142,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>709</v>
       </c>
@@ -5172,7 +5171,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>198</v>
       </c>
@@ -5230,7 +5229,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>294</v>
       </c>
@@ -5288,7 +5287,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>184</v>
       </c>
@@ -5317,7 +5316,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>294</v>
       </c>
@@ -5346,7 +5345,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>700</v>
       </c>
@@ -5404,7 +5403,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>733</v>
       </c>
@@ -5433,7 +5432,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>653</v>
       </c>
@@ -5462,7 +5461,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>20</v>
       </c>
@@ -5491,7 +5490,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>294</v>
       </c>
@@ -5549,7 +5548,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>760</v>
       </c>
@@ -5607,7 +5606,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>294</v>
       </c>
@@ -5636,7 +5635,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>193</v>
       </c>
@@ -5665,7 +5664,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>244</v>
       </c>
@@ -5723,7 +5722,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>843</v>
       </c>
@@ -5781,7 +5780,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>733</v>
       </c>
@@ -5810,7 +5809,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>219</v>
       </c>
@@ -5839,7 +5838,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>198</v>
       </c>
@@ -5868,7 +5867,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>264</v>
       </c>
@@ -5926,7 +5925,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>863</v>
       </c>
@@ -5961,7 +5960,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>570</v>
       </c>
@@ -6019,7 +6018,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>375</v>
       </c>
@@ -6077,7 +6076,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="102" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>806</v>
       </c>
@@ -6106,7 +6105,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>806</v>
       </c>
@@ -6156,7 +6155,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>630</v>
       </c>
@@ -6185,7 +6184,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="105" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>865</v>
       </c>
@@ -6278,7 +6277,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>264</v>
       </c>
@@ -6336,7 +6335,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>653</v>
       </c>
@@ -6365,7 +6364,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>20</v>
       </c>
@@ -6394,7 +6393,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>20</v>
       </c>
@@ -6452,7 +6451,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="114" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>198</v>
       </c>
@@ -6481,7 +6480,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>760</v>
       </c>
@@ -6510,7 +6509,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>806</v>
       </c>
@@ -6539,7 +6538,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>510</v>
       </c>
@@ -6568,7 +6567,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>105</v>
       </c>
@@ -6676,7 +6675,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>806</v>
       </c>
@@ -6705,7 +6704,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>806</v>
       </c>
@@ -6740,7 +6739,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>294</v>
       </c>
@@ -6833,7 +6832,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>672</v>
       </c>
@@ -6862,7 +6861,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>806</v>
       </c>
@@ -6891,7 +6890,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>20</v>
       </c>
@@ -6926,7 +6925,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>92</v>
       </c>
@@ -7042,7 +7041,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>733</v>
       </c>
@@ -7100,7 +7099,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>198</v>
       </c>
@@ -7129,7 +7128,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>806</v>
       </c>
@@ -7187,7 +7186,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>580</v>
       </c>
@@ -7216,7 +7215,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>806</v>
       </c>
@@ -7245,7 +7244,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>798</v>
       </c>
@@ -7303,7 +7302,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="142" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>843</v>
       </c>
@@ -7361,7 +7360,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>843</v>
       </c>
@@ -7390,7 +7389,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="145" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>294</v>
       </c>
@@ -7419,7 +7418,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>294</v>
       </c>
@@ -7448,7 +7447,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="147" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>601</v>
       </c>
@@ -7506,7 +7505,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="149" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>561</v>
       </c>
@@ -7535,7 +7534,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="150" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>20</v>
       </c>
@@ -7593,7 +7592,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="152" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>700</v>
       </c>
@@ -7622,7 +7621,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>510</v>
       </c>
@@ -7651,7 +7650,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>617</v>
       </c>
@@ -7730,7 +7729,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="156" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>690</v>
       </c>
@@ -7788,7 +7787,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>733</v>
       </c>
@@ -7817,7 +7816,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="159" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>495</v>
       </c>
@@ -7846,7 +7845,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>617</v>
       </c>
@@ -7875,7 +7874,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="161" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>681</v>
       </c>
@@ -7933,7 +7932,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="163" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>198</v>
       </c>
@@ -7962,7 +7961,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="164" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>20</v>
       </c>
@@ -7991,7 +7990,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="165" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>375</v>
       </c>
@@ -8020,7 +8019,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="166" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>843</v>
       </c>
@@ -8049,7 +8048,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="167" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>733</v>
       </c>
@@ -8107,7 +8106,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="169" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>653</v>
       </c>
@@ -8136,7 +8135,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="170" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>63</v>
       </c>
@@ -8165,7 +8164,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>193</v>
       </c>
@@ -8194,7 +8193,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="172" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>595</v>
       </c>
@@ -8223,7 +8222,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="173" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>769</v>
       </c>
@@ -8252,7 +8251,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="174" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>760</v>
       </c>
@@ -8281,7 +8280,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>501</v>
       </c>
@@ -8310,7 +8309,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>561</v>
       </c>
@@ -8339,7 +8338,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>20</v>
       </c>
@@ -8368,7 +8367,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="178" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>601</v>
       </c>
@@ -8397,7 +8396,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="179" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>570</v>
       </c>
@@ -8455,7 +8454,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="181" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>617</v>
       </c>
@@ -8534,7 +8533,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="183" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>733</v>
       </c>
@@ -8563,7 +8562,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="184" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>264</v>
       </c>
@@ -8592,7 +8591,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="185" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>561</v>
       </c>
@@ -8621,7 +8620,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="186" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>375</v>
       </c>
@@ -8650,7 +8649,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="187" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>760</v>
       </c>
@@ -8679,7 +8678,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="188" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>806</v>
       </c>
@@ -8729,7 +8728,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="189" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>294</v>
       </c>
@@ -8758,7 +8757,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="190" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>760</v>
       </c>
@@ -8787,7 +8786,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="191" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>440</v>
       </c>
@@ -8845,7 +8844,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="193" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>264</v>
       </c>
@@ -8874,7 +8873,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="194" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>294</v>
       </c>
@@ -8932,7 +8931,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="196" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>198</v>
       </c>
@@ -8961,7 +8960,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="197" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>375</v>
       </c>
@@ -8990,7 +8989,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="198" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>733</v>
       </c>
@@ -9019,7 +9018,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="199" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>455</v>
       </c>
@@ -9048,7 +9047,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="200" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>198</v>
       </c>
@@ -9083,7 +9082,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="201" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>20</v>
       </c>
@@ -9112,7 +9111,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="202" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>264</v>
       </c>
@@ -9141,7 +9140,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="203" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>294</v>
       </c>
@@ -9170,7 +9169,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="204" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>733</v>
       </c>
@@ -9199,7 +9198,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="205" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>244</v>
       </c>
@@ -9228,7 +9227,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="206" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>286</v>
       </c>
@@ -9286,7 +9285,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="208" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>244</v>
       </c>
@@ -9315,7 +9314,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="209" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>700</v>
       </c>
@@ -9344,7 +9343,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="210" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>256</v>
       </c>
@@ -9373,7 +9372,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="211" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>637</v>
       </c>
@@ -9402,7 +9401,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="212" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>264</v>
       </c>
@@ -9431,7 +9430,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="213" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>105</v>
       </c>
@@ -9460,7 +9459,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="214" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>440</v>
       </c>
@@ -9489,7 +9488,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="215" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>20</v>
       </c>
@@ -9518,7 +9517,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="216" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>700</v>
       </c>
@@ -9576,7 +9575,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="218" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>20</v>
       </c>
@@ -9605,7 +9604,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="219" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>510</v>
       </c>
@@ -9634,7 +9633,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="220" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>653</v>
       </c>
@@ -9692,7 +9691,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="222" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>294</v>
       </c>
@@ -9721,7 +9720,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="223" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>219</v>
       </c>
@@ -9750,7 +9749,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="224" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>48</v>
       </c>
@@ -9779,7 +9778,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="225" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>264</v>
       </c>
@@ -9808,7 +9807,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="226" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>455</v>
       </c>
@@ -9837,7 +9836,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="227" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>533</v>
       </c>
@@ -9866,7 +9865,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="228" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>264</v>
       </c>
@@ -9916,7 +9915,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="229" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>294</v>
       </c>
@@ -10032,7 +10031,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="233" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>877</v>
       </c>
@@ -10067,7 +10066,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="234" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>198</v>
       </c>
@@ -10096,7 +10095,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="235" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>580</v>
       </c>
@@ -10154,7 +10153,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="237" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>452</v>
       </c>
@@ -10183,7 +10182,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="238" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>20</v>
       </c>
@@ -10218,7 +10217,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="239" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>244</v>
       </c>
@@ -10247,7 +10246,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="240" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>294</v>
       </c>
@@ -10276,7 +10275,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="241" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>455</v>
       </c>
@@ -10305,7 +10304,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="242" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>244</v>
       </c>
@@ -10334,7 +10333,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="243" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>294</v>
       </c>
@@ -10363,7 +10362,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="244" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>792</v>
       </c>
@@ -10392,7 +10391,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="245" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>806</v>
       </c>
@@ -10421,7 +10420,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="246" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>806</v>
       </c>
@@ -10450,7 +10449,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="247" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>769</v>
       </c>
@@ -10479,7 +10478,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="248" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>601</v>
       </c>
@@ -10508,7 +10507,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="249" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>510</v>
       </c>
@@ -10537,7 +10536,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="250" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>105</v>
       </c>
@@ -10566,7 +10565,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="251" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>92</v>
       </c>
@@ -10595,7 +10594,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="252" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>294</v>
       </c>
@@ -10653,7 +10652,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="254" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>510</v>
       </c>
@@ -10682,7 +10681,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="255" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>244</v>
       </c>
@@ -10711,7 +10710,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="256" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>806</v>
       </c>
@@ -10761,7 +10760,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="257" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>455</v>
       </c>
@@ -10819,7 +10818,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="259" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>601</v>
       </c>
@@ -10848,7 +10847,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="260" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>361</v>
       </c>
@@ -10906,7 +10905,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="262" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>244</v>
       </c>
@@ -10935,7 +10934,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="263" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>294</v>
       </c>
@@ -10964,7 +10963,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="264" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>294</v>
       </c>
@@ -10993,7 +10992,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="265" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>637</v>
       </c>
@@ -11022,7 +11021,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="266" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>843</v>
       </c>
@@ -11072,7 +11071,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="267" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>294</v>
       </c>
@@ -11101,7 +11100,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="268" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>198</v>
       </c>
@@ -11130,7 +11129,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="269" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>806</v>
       </c>
@@ -11159,7 +11158,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="270" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>806</v>
       </c>
@@ -11223,7 +11222,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="272" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>294</v>
       </c>
@@ -11252,7 +11251,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="273" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>709</v>
       </c>
@@ -11281,7 +11280,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="274" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>294</v>
       </c>
@@ -11331,7 +11330,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="275" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>440</v>
       </c>
@@ -11360,7 +11359,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="276" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>510</v>
       </c>
@@ -11389,7 +11388,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="277" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>588</v>
       </c>
@@ -11468,7 +11467,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="279" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>681</v>
       </c>
@@ -11497,7 +11496,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="280" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>510</v>
       </c>
@@ -11584,7 +11583,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="283" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>672</v>
       </c>
@@ -11613,7 +11612,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="284" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>510</v>
       </c>
@@ -11671,7 +11670,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="286" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>806</v>
       </c>
@@ -11700,7 +11699,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="287" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>843</v>
       </c>
@@ -11729,7 +11728,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="288" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>294</v>
       </c>
@@ -11758,7 +11757,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="289" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>601</v>
       </c>
@@ -11787,7 +11786,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="290" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>672</v>
       </c>
@@ -11845,7 +11844,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="292" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>690</v>
       </c>
@@ -11903,7 +11902,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="294" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>806</v>
       </c>
@@ -11932,7 +11931,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="295" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>595</v>
       </c>
@@ -11961,7 +11960,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="296" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>510</v>
       </c>
@@ -11990,7 +11989,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="297" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>510</v>
       </c>
@@ -12019,7 +12018,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="298" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>570</v>
       </c>
@@ -12077,7 +12076,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="300" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>709</v>
       </c>
@@ -12106,7 +12105,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="301" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>286</v>
       </c>
@@ -12135,7 +12134,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="302" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>184</v>
       </c>
@@ -12193,7 +12192,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="304" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>760</v>
       </c>
@@ -12222,7 +12221,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="305" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>495</v>
       </c>
@@ -12251,7 +12250,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="306" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>630</v>
       </c>
@@ -12309,7 +12308,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="308" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>48</v>
       </c>
@@ -12338,7 +12337,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="309" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>455</v>
       </c>
@@ -12367,7 +12366,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="310" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>294</v>
       </c>
@@ -12396,7 +12395,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="311" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>843</v>
       </c>
@@ -12425,7 +12424,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="312" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>198</v>
       </c>
@@ -12454,7 +12453,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="313" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>375</v>
       </c>
@@ -12512,7 +12511,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="315" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>375</v>
       </c>
@@ -12562,7 +12561,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="316" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>806</v>
       </c>
@@ -12597,7 +12596,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="317" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>294</v>
       </c>
@@ -12626,7 +12625,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="318" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>193</v>
       </c>
@@ -12655,7 +12654,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="319" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>855</v>
       </c>
@@ -12713,7 +12712,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="321" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>260</v>
       </c>
@@ -12800,7 +12799,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="324" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>690</v>
       </c>
@@ -12829,7 +12828,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="325" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>601</v>
       </c>
@@ -12858,7 +12857,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="326" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>294</v>
       </c>
@@ -12887,7 +12886,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="327" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>375</v>
       </c>
@@ -12916,7 +12915,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="328" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>244</v>
       </c>
@@ -12945,7 +12944,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="329" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>855</v>
       </c>
@@ -12974,7 +12973,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="330" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>92</v>
       </c>
@@ -13032,7 +13031,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="332" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>877</v>
       </c>
@@ -13067,7 +13066,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="333" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>282</v>
       </c>
@@ -13125,7 +13124,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="335" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>63</v>
       </c>
@@ -13154,7 +13153,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="336" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>688</v>
       </c>
@@ -13204,7 +13203,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="337" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>375</v>
       </c>
@@ -13262,7 +13261,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="339" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>282</v>
       </c>
@@ -13320,7 +13319,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="341" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>184</v>
       </c>
@@ -13407,7 +13406,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="344" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>653</v>
       </c>
@@ -13436,7 +13435,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="345" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>806</v>
       </c>
@@ -13486,7 +13485,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="346" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>504</v>
       </c>
@@ -13515,7 +13514,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="347" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>495</v>
       </c>
@@ -13573,7 +13572,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="349" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>219</v>
       </c>
@@ -13602,7 +13601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="350" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>294</v>
       </c>
@@ -13631,7 +13630,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="351" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>219</v>
       </c>
@@ -13660,7 +13659,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="352" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>294</v>
       </c>
@@ -13776,7 +13775,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="356" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>198</v>
       </c>
@@ -13834,7 +13833,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="358" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>867</v>
       </c>
@@ -13869,7 +13868,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="359" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>653</v>
       </c>
@@ -13898,7 +13897,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="360" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>20</v>
       </c>
@@ -13927,7 +13926,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="361" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>733</v>
       </c>
@@ -13956,7 +13955,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="362" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>294</v>
       </c>
@@ -13985,7 +13984,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="363" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>294</v>
       </c>
@@ -14122,7 +14121,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="367" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>294</v>
       </c>
@@ -14151,7 +14150,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="368" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>63</v>
       </c>
@@ -14180,7 +14179,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="369" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>700</v>
       </c>
@@ -14259,7 +14258,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="371" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>637</v>
       </c>
@@ -14346,7 +14345,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="374" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>48</v>
       </c>
@@ -14375,7 +14374,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="375" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>294</v>
       </c>
@@ -14433,7 +14432,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="377" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>48</v>
       </c>
@@ -14491,7 +14490,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="379" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>806</v>
       </c>
@@ -14520,7 +14519,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="380" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>570</v>
       </c>
@@ -14549,7 +14548,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="381" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>510</v>
       </c>
@@ -14578,7 +14577,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="382" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>375</v>
       </c>
@@ -14607,7 +14606,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="383" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>264</v>
       </c>
@@ -14752,7 +14751,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="388" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>806</v>
       </c>
@@ -14781,7 +14780,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="389" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>264</v>
       </c>
@@ -14810,7 +14809,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="390" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>637</v>
       </c>
@@ -14839,7 +14838,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="391" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>617</v>
       </c>
@@ -14868,7 +14867,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="392" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>440</v>
       </c>
@@ -14897,7 +14896,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="393" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>375</v>
       </c>
@@ -14926,7 +14925,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="394" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>16</v>
       </c>
@@ -15158,7 +15157,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="402" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>595</v>
       </c>
@@ -15187,7 +15186,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="403" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>733</v>
       </c>
@@ -15316,7 +15315,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="406" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>806</v>
       </c>
@@ -15345,7 +15344,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="407" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>867</v>
       </c>
@@ -15459,7 +15458,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="410" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>510</v>
       </c>
@@ -15488,7 +15487,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="411" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>601</v>
       </c>
@@ -15517,7 +15516,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="412" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>672</v>
       </c>
@@ -15596,7 +15595,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="414" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>798</v>
       </c>
@@ -15625,7 +15624,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="415" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>294</v>
       </c>
@@ -15654,7 +15653,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="416" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>806</v>
       </c>
@@ -15683,7 +15682,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="417" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>617</v>
       </c>
@@ -15791,7 +15790,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="420" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>653</v>
       </c>
@@ -15820,7 +15819,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="421" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>219</v>
       </c>
@@ -15849,7 +15848,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="422" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>375</v>
       </c>
@@ -15878,7 +15877,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="423" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>260</v>
       </c>
@@ -15907,7 +15906,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="424" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>294</v>
       </c>
@@ -15936,7 +15935,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="425" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>865</v>
       </c>
@@ -15971,7 +15970,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="426" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>601</v>
       </c>
@@ -16000,7 +15999,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="427" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>617</v>
       </c>
@@ -16029,7 +16028,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="428" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>588</v>
       </c>
@@ -16058,7 +16057,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="429" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>264</v>
       </c>
@@ -16087,7 +16086,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="430" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>105</v>
       </c>
@@ -16116,7 +16115,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="431" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>440</v>
       </c>
@@ -16145,7 +16144,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="432" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>806</v>
       </c>
@@ -16174,7 +16173,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="433" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>375</v>
       </c>
@@ -16203,7 +16202,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="434" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>264</v>
       </c>
@@ -16232,7 +16231,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="435" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>286</v>
       </c>
@@ -16261,7 +16260,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="436" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>588</v>
       </c>
@@ -16311,7 +16310,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="437" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>798</v>
       </c>
@@ -16340,7 +16339,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="438" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>375</v>
       </c>
@@ -16369,7 +16368,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="439" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>73</v>
       </c>
@@ -16398,7 +16397,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="440" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>653</v>
       </c>
@@ -16427,7 +16426,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="441" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>709</v>
       </c>
@@ -16485,7 +16484,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="443" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>264</v>
       </c>
@@ -16514,7 +16513,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="444" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>501</v>
       </c>
@@ -16543,7 +16542,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="445" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>806</v>
       </c>
@@ -16672,7 +16671,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="448" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>561</v>
       </c>
@@ -16722,7 +16721,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="449" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>806</v>
       </c>
@@ -16809,7 +16808,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="452" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>637</v>
       </c>
@@ -16838,7 +16837,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="453" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>63</v>
       </c>
@@ -16896,7 +16895,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="455" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>798</v>
       </c>
@@ -17004,7 +17003,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="458" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>806</v>
       </c>
@@ -17039,7 +17038,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="459" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>561</v>
       </c>
@@ -17068,7 +17067,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="460" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>806</v>
       </c>
@@ -17097,7 +17096,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="461" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>455</v>
       </c>
@@ -17176,7 +17175,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="463" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>561</v>
       </c>
@@ -17205,7 +17204,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="464" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>375</v>
       </c>
@@ -17255,7 +17254,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="465" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>861</v>
       </c>
@@ -17371,7 +17370,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="469" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>294</v>
       </c>
@@ -17400,7 +17399,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="470" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>806</v>
       </c>
@@ -17450,7 +17449,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="471" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>294</v>
       </c>
@@ -17479,7 +17478,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="472" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>690</v>
       </c>
@@ -17508,7 +17507,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="473" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>375</v>
       </c>
@@ -17537,7 +17536,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="474" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>601</v>
       </c>
@@ -17566,7 +17565,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="475" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>367</v>
       </c>
@@ -17595,7 +17594,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="476" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>92</v>
       </c>
@@ -17645,7 +17644,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="477" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>672</v>
       </c>
@@ -17674,7 +17673,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="478" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>559</v>
       </c>
@@ -17703,7 +17702,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="479" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>653</v>
       </c>
@@ -17732,7 +17731,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="480" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>294</v>
       </c>
@@ -17761,7 +17760,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="481" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>733</v>
       </c>
@@ -17790,7 +17789,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="482" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>792</v>
       </c>
@@ -17840,7 +17839,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="483" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>20</v>
       </c>
@@ -17869,7 +17868,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="484" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>888</v>
       </c>
@@ -17904,7 +17903,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="485" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>769</v>
       </c>
@@ -17933,7 +17932,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="486" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>184</v>
       </c>
@@ -17962,7 +17961,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="487" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>504</v>
       </c>
@@ -17991,7 +17990,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="488" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>798</v>
       </c>
@@ -18020,7 +18019,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="489" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>294</v>
       </c>
@@ -18049,7 +18048,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="490" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>843</v>
       </c>
@@ -18078,7 +18077,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="491" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>877</v>
       </c>
@@ -18113,7 +18112,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="492" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>733</v>
       </c>
@@ -18142,7 +18141,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="493" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>792</v>
       </c>
@@ -18229,7 +18228,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="496" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>617</v>
       </c>
@@ -18287,7 +18286,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="498" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>637</v>
       </c>
@@ -18316,7 +18315,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="499" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>570</v>
       </c>
@@ -18345,7 +18344,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="500" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>681</v>
       </c>
@@ -18374,7 +18373,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="501" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>455</v>
       </c>
@@ -18403,7 +18402,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="502" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>449</v>
       </c>
@@ -18432,7 +18431,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="503" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>198</v>
       </c>
@@ -18461,7 +18460,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="504" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>806</v>
       </c>
@@ -18540,7 +18539,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="506" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>367</v>
       </c>
@@ -18627,7 +18626,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="509" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>637</v>
       </c>
@@ -18656,7 +18655,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="510" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>653</v>
       </c>
@@ -18685,7 +18684,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="511" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>630</v>
       </c>
@@ -18714,7 +18713,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="512" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>700</v>
       </c>
@@ -18743,7 +18742,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="513" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>20</v>
       </c>
@@ -18772,7 +18771,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="514" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>48</v>
       </c>
@@ -18801,7 +18800,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="515" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>601</v>
       </c>
@@ -18830,7 +18829,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="516" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>294</v>
       </c>
@@ -18980,7 +18979,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="519" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>637</v>
       </c>
@@ -19009,7 +19008,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="520" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>653</v>
       </c>
@@ -19096,7 +19095,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="523" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>855</v>
       </c>
@@ -19175,7 +19174,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="525" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>294</v>
       </c>
@@ -19204,7 +19203,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="526" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>440</v>
       </c>
@@ -19233,7 +19232,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="527" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>184</v>
       </c>
@@ -19262,7 +19261,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="528" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>48</v>
       </c>
@@ -19291,7 +19290,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="529" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>690</v>
       </c>
@@ -19320,7 +19319,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="530" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>806</v>
       </c>
@@ -19349,7 +19348,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="531" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>375</v>
       </c>
@@ -19378,7 +19377,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="532" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>63</v>
       </c>
@@ -19407,7 +19406,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="533" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>219</v>
       </c>
@@ -19523,7 +19522,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="537" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>264</v>
       </c>
@@ -19552,7 +19551,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="538" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>20</v>
       </c>
@@ -19581,7 +19580,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="539" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>219</v>
       </c>
@@ -19631,7 +19630,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="540" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>601</v>
       </c>
@@ -19681,7 +19680,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="541" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>294</v>
       </c>
@@ -19731,7 +19730,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="542" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>105</v>
       </c>
@@ -19760,7 +19759,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="543" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>198</v>
       </c>
@@ -19789,7 +19788,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="544" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>294</v>
       </c>
@@ -19847,7 +19846,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="546" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>294</v>
       </c>
@@ -19876,7 +19875,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="547" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>843</v>
       </c>
@@ -19905,7 +19904,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="548" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>105</v>
       </c>
@@ -19963,7 +19962,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="550" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>294</v>
       </c>
@@ -19992,7 +19991,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="551" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>73</v>
       </c>
@@ -20079,7 +20078,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="554" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>672</v>
       </c>
@@ -20137,7 +20136,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="556" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>580</v>
       </c>
@@ -20166,7 +20165,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="557" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>20</v>
       </c>
@@ -20195,7 +20194,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="558" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>184</v>
       </c>
@@ -20253,7 +20252,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="560" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>617</v>
       </c>
@@ -20311,7 +20310,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="562" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>198</v>
       </c>
@@ -20340,7 +20339,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="563" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>48</v>
       </c>
@@ -20369,7 +20368,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="564" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>843</v>
       </c>
@@ -20398,7 +20397,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="565" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>617</v>
       </c>
@@ -20456,7 +20455,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="567" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>105</v>
       </c>
@@ -20485,7 +20484,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="568" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>20</v>
       </c>
@@ -20514,7 +20513,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="569" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>219</v>
       </c>
@@ -20564,7 +20563,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="570" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>20</v>
       </c>
@@ -20593,7 +20592,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="571" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>510</v>
       </c>
@@ -20622,7 +20621,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="572" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>198</v>
       </c>
@@ -20651,7 +20650,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="573" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>733</v>
       </c>
@@ -20680,7 +20679,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="574" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>361</v>
       </c>
@@ -20709,7 +20708,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="575" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>533</v>
       </c>
@@ -20759,7 +20758,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="576" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>595</v>
       </c>
@@ -20788,7 +20787,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="577" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>769</v>
       </c>
@@ -20817,7 +20816,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="578" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>510</v>
       </c>
@@ -20975,7 +20974,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="582" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>733</v>
       </c>
@@ -21033,7 +21032,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="584" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>244</v>
       </c>
@@ -21062,7 +21061,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="585" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>733</v>
       </c>
@@ -21091,7 +21090,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="586" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>294</v>
       </c>
@@ -21149,7 +21148,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="588" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>601</v>
       </c>
@@ -21178,7 +21177,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="589" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>184</v>
       </c>
@@ -21207,7 +21206,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="590" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>588</v>
       </c>
@@ -21265,7 +21264,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="592" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>286</v>
       </c>
@@ -21294,7 +21293,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="593" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>198</v>
       </c>
@@ -21323,7 +21322,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="594" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>533</v>
       </c>
@@ -21352,7 +21351,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="595" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>630</v>
       </c>
@@ -21381,7 +21380,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="596" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>294</v>
       </c>
@@ -21410,7 +21409,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="597" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>375</v>
       </c>
@@ -21439,7 +21438,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="598" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>294</v>
       </c>
@@ -21468,7 +21467,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="599" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>690</v>
       </c>
@@ -21497,7 +21496,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="600" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>495</v>
       </c>
@@ -21555,7 +21554,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="602" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>294</v>
       </c>
@@ -21584,7 +21583,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="603" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>570</v>
       </c>
@@ -21613,7 +21612,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="604" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>294</v>
       </c>
@@ -21700,7 +21699,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="607" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>653</v>
       </c>
@@ -21729,7 +21728,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="608" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>294</v>
       </c>
@@ -21758,7 +21757,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="609" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>367</v>
       </c>
@@ -21787,7 +21786,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="610" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>733</v>
       </c>
@@ -21816,7 +21815,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="611" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>588</v>
       </c>
@@ -21845,7 +21844,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="612" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>806</v>
       </c>
@@ -21903,7 +21902,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="614" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>375</v>
       </c>
@@ -21932,7 +21931,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="615" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>20</v>
       </c>
@@ -21990,7 +21989,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="617" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>533</v>
       </c>
@@ -22069,7 +22068,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="619" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>681</v>
       </c>
@@ -22098,7 +22097,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="620" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>533</v>
       </c>
@@ -22127,7 +22126,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="621" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>653</v>
       </c>
@@ -22156,7 +22155,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="622" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>630</v>
       </c>
@@ -22185,7 +22184,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="623" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>510</v>
       </c>
@@ -22214,7 +22213,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="624" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>798</v>
       </c>
@@ -22272,7 +22271,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="626" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>637</v>
       </c>
@@ -22301,7 +22300,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="627" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>20</v>
       </c>
@@ -22330,7 +22329,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="628" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>769</v>
       </c>
@@ -22417,7 +22416,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="631" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>20</v>
       </c>
@@ -22446,7 +22445,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="632" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>294</v>
       </c>
@@ -22475,7 +22474,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="633" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>294</v>
       </c>
@@ -22525,7 +22524,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="634" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>440</v>
       </c>
@@ -22612,7 +22611,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="637" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>375</v>
       </c>
@@ -22670,7 +22669,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="639" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>256</v>
       </c>
@@ -22699,7 +22698,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="640" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>733</v>
       </c>
@@ -22786,7 +22785,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="643" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>700</v>
       </c>
@@ -22836,7 +22835,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="644" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>806</v>
       </c>
@@ -22886,7 +22885,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="645" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>48</v>
       </c>
@@ -22936,7 +22935,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="646" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>286</v>
       </c>
@@ -22986,7 +22985,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="647" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>504</v>
       </c>
@@ -23036,7 +23035,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="648" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>367</v>
       </c>
@@ -23086,7 +23085,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="649" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>495</v>
       </c>
@@ -23136,7 +23135,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="650" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>733</v>
       </c>
@@ -23186,7 +23185,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="651" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>672</v>
       </c>
@@ -23236,7 +23235,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="652" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>806</v>
       </c>
@@ -23286,7 +23285,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="653" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>20</v>
       </c>
@@ -23336,7 +23335,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="654" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>375</v>
       </c>
@@ -23386,7 +23385,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="655" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>637</v>
       </c>
@@ -23436,7 +23435,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="656" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>792</v>
       </c>
@@ -23515,7 +23514,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="658" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>504</v>
       </c>
@@ -23623,7 +23622,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="661" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>440</v>
       </c>
@@ -23702,7 +23701,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="663" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>504</v>
       </c>
@@ -23752,7 +23751,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="664" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>580</v>
       </c>
@@ -23802,7 +23801,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="665" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>294</v>
       </c>
@@ -23852,7 +23851,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="666" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>681</v>
       </c>
@@ -23902,7 +23901,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="667" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>637</v>
       </c>
@@ -23952,7 +23951,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="668" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>637</v>
       </c>
@@ -24002,7 +24001,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="669" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>286</v>
       </c>
@@ -24052,7 +24051,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="670" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>733</v>
       </c>
@@ -24102,7 +24101,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="671" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>637</v>
       </c>
@@ -24152,7 +24151,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="672" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>617</v>
       </c>
@@ -24202,7 +24201,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="673" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>244</v>
       </c>
@@ -24252,7 +24251,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="674" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>570</v>
       </c>
@@ -24302,7 +24301,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="675" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>48</v>
       </c>
@@ -24352,7 +24351,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="676" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>294</v>
       </c>
@@ -24402,7 +24401,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="677" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>367</v>
       </c>
@@ -24452,7 +24451,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="678" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>510</v>
       </c>
@@ -24502,9 +24501,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="679" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>361</v>
+        <v>400</v>
       </c>
       <c r="B679" t="s">
         <v>362</v>
@@ -24552,7 +24551,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="680" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>769</v>
       </c>
@@ -24631,7 +24630,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="682" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>637</v>
       </c>
@@ -24681,7 +24680,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="683" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>733</v>
       </c>
@@ -24731,7 +24730,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="684" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>653</v>
       </c>
@@ -24781,7 +24780,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="685" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>92</v>
       </c>
@@ -24831,7 +24830,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="686" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>92</v>
       </c>
@@ -24881,7 +24880,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="687" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>769</v>
       </c>
@@ -24931,7 +24930,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="688" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>733</v>
       </c>
@@ -25010,7 +25009,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="690" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>690</v>
       </c>
@@ -25060,7 +25059,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="691" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>601</v>
       </c>
@@ -25110,7 +25109,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="692" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>570</v>
       </c>
@@ -25160,7 +25159,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="693" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>294</v>
       </c>
@@ -25241,19 +25240,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:P694" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Belgium"/>
-        <filter val="Brazil"/>
-        <filter val="Colombia"/>
-        <filter val="France"/>
-        <filter val="Germany"/>
-        <filter val="Italy"/>
-        <filter val="Netherlands"/>
-        <filter val="Spain"/>
-        <filter val="Turkey"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P694">
       <sortCondition ref="A1:A694"/>
     </sortState>
